--- a/Spider_XHS/datas/excel_datas/5c615e71000000001a023286.xlsx
+++ b/Spider_XHS/datas/excel_datas/5c615e71000000001a023286.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/688585f70000000010026526?xsec_token=ABQ8UOTjsf001OHEETN9YwvCO_oZ9RDKYkkCE5_YsJwXI=</t>
+          <t>https://www.xiaohongshu.com/explore/688585f70000000010026526?xsec_token=ABQ8UOTjsf001OHEETN9YwvPmTzyiJSdmEcMpxG37jMpA=</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/ef3c2246c9310d3163db5d80609aab72/notes_pre_post/1040g3k831ke1sja82ai05n31bpomkck6edd10o8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/6f4251089ad34ec4e87b0870e221ce7c/notes_pre_post/1040g3k831ke1sja82aig5n31bpomkck6is81p3o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/79fc5ed386f4fec221969dc90642984c/notes_pre_post/1040g3k831ke1sja82aj05n31bpomkck6s7tui10!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/07d346813b434e2ec929540d009c1f8b/notes_pre_post/1040g3k831ke1sja82ajg5n31bpomkck6u3pn0d8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/2dbb83a7891f4c881de90b3cae3fe7df/notes_pre_post/1040g3k831ke1sja82ak05n31bpomkck6maedl6g!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/a715c4e40ddf683c428c4d14f8002988/notes_pre_post/1040g3k831ke1sja82akg5n31bpomkck64blen88!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/2633eff7077e4af346d47352c99d9f51/notes_pre_post/1040g3k831ke2n6ijk8705n31bpomkck6k5t6au8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/dd425e13b64e21dc069da01359a691a2/notes_pre_post/1040g3k831ke2n6ijk87g5n31bpomkck620cncbg!nd_dft_wlteh_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/76a1221f717fa7c25413fa9a013da3a0/notes_pre_post/1040g3k831ke1sja82ai05n31bpomkck6edd10o8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/6421d0b3b24e9c4b870d793ea170bc2e/notes_pre_post/1040g3k831ke1sja82aig5n31bpomkck6is81p3o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/e9d415eff679fb86192f5293676bcfb3/notes_pre_post/1040g3k831ke1sja82aj05n31bpomkck6s7tui10!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/6234e554c8c2fd64ae88dea4e9dd2b0b/notes_pre_post/1040g3k831ke1sja82ajg5n31bpomkck6u3pn0d8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/a28dfad765ef759a53912197684df038/notes_pre_post/1040g3k831ke1sja82ak05n31bpomkck6maedl6g!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/1d05d7defd1e3d3cd751df677491847f/notes_pre_post/1040g3k831ke1sja82akg5n31bpomkck64blen88!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/a74913175048701d6a7054434a08dbe3/notes_pre_post/1040g3k831ke2n6ijk8705n31bpomkck6k5t6au8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/ee7b393f230971040e939e7cb21f68c2/notes_pre_post/1040g3k831ke2n6ijk87g5n31bpomkck620cncbg!nd_dft_wlteh_webp_3']</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/6873ad9a00000000100130c0?xsec_token=ABdWMXzvZ_-3oxYtVb99bGlxaOB5x_scESNIJmniko_c0=</t>
+          <t>https://www.xiaohongshu.com/explore/6873ad9a00000000100130c0?xsec_token=ABdWMXzvZ_-3oxYtVb99bGl50zKRmIupZopUStxxxDYCw=</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/296b0064078987c4e039d1fd1657762f/notes_pre_post/1040g3k031jsl04on3q005n31bpomkck6c35t2j0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/373d2983b8863071f1d45cf144e801da/notes_pre_post/1040g3k031jsl04on3q0g5n31bpomkck69p3gjsg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/93b6b588431974bffb2af102253f8ab2/notes_pre_post/1040g3k031jsl04on3q105n31bpomkck60ph1too!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/3f577e680f3144e6313eeca30cb25f86/notes_pre_post/1040g3k031jsl04on3q1g5n31bpomkck6g08bs10!nd_dft_wlteh_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/2f3bc7be91ca63af2cc88a794a06cafe/notes_pre_post/1040g3k031jsl04on3q005n31bpomkck6c35t2j0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/e4aa8c56f690d075c8bc019554cafdf6/notes_pre_post/1040g3k031jsl04on3q0g5n31bpomkck69p3gjsg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/4a3284367089d7ac63885883f972f478/notes_pre_post/1040g3k031jsl04on3q105n31bpomkck60ph1too!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/8866fa726acfd17b4a0b8f709a9e2ff0/notes_pre_post/1040g3k031jsl04on3q1g5n31bpomkck6g08bs10!nd_dft_wlteh_webp_3']</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/67bc5b9b000000002503d918?xsec_token=ABXGPrjaobpJOj-GyNlEqKn6f39iTEHhLzajsHnVIsAYo=</t>
+          <t>https://www.xiaohongshu.com/explore/67bc5b9b000000002503d918?xsec_token=ABXGPrjaobpJOj-GyNlEqKn5QwVkecNVES_ZTJ85VmSZU=</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/af18bb28fc9afdbbdd137f77287063a6/1040g00831e9kdkkngc005n31bpomkck6apk6k7o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/9fe986c15fd9de186b85938c78552a7a/1040g00831e9kdkkngc0g5n31bpomkck6npgo5t8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/4c250ae32dfb8d088e2b0ac1a568c63b/1040g00831e9kdkkngc105n31bpomkck6n64n4mg!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/2659fc52926ab75844784806cd946d95/1040g00831e9kdkkngc1g5n31bpomkck6jqit1go!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/f154faf3cc694cdde1bb29974d266c8c/1040g00831e9kdkkngc205n31bpomkck6fcmcq80!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/b9f099b88dce1fab05490b5816acb60f/1040g00831e9kdkkngc2g5n31bpomkck69pmgu48!nd_dft_wlteh_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/07cfcfa7fc5f2cfd7a1ecc545ce00f0f/1040g00831e9kdkkngc005n31bpomkck6apk6k7o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/8d54ba2ac1f195391a4ce022b9c43230/1040g00831e9kdkkngc0g5n31bpomkck6npgo5t8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/980fd77eb9f9820ff672f73f3f781cdc/1040g00831e9kdkkngc105n31bpomkck6n64n4mg!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/3c8951bed5dbbb37720cb3b1bfd25945/1040g00831e9kdkkngc1g5n31bpomkck6jqit1go!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/61e10653296cdf6624d8980c105bca2d/1040g00831e9kdkkngc205n31bpomkck6fcmcq80!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/20730873639ca5cc40ee224a0956cd98/1040g00831e9kdkkngc2g5n31bpomkck69pmgu48!nd_dft_wlteh_webp_3']</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/67026a45000000001a020499?xsec_token=ABM_irCpxhS3pY5IaXWQDOGmRFghFXYDnohkkWfAeoBIo=</t>
+          <t>https://www.xiaohongshu.com/explore/67026a45000000001a020499?xsec_token=ABM_irCpxhS3pY5IaXWQDOGiC5yDWnf2Wn7YlFVILWeT4=</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/98760789634d4ee953419d111d9627eb/1040g008318k1mq4mgs005n31bpomkck6qnkaa60!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/8fedf3284073aaaff146243d2fb9547d/1040g008318k1mq4mgs0g5n31bpomkck6u62lekg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/773d49345686b27f294405179e1827e1/1040g008318k1mq4mgs105n31bpomkck6b7kbi40!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/8e05438d34c44e2debdf743ccaa6deb7/1040g008318k1mq4mgs1g5n31bpomkck6led3kbo!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/7bacccfe8f8a1f36c5939638e518ac9b/1040g008318k1mq4mgs205n31bpomkck66v82j7g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/df27970a575ae855739ee22a97c41e0b/1040g008318k1mq4mgs2g5n31bpomkck6344rci0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/9c391262301110dec0c175d34d192540/1040g008318k1mq4mgs305n31bpomkck6abqlmfg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/cf99b29409c52ba33b6e038de870d10b/1040g008318k1mq4mgs3g5n31bpomkck6j3lj1n8!nd_dft_wgth_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/cd26c4532c22100c89301ed81b218653/1040g008318k1mq4mgs005n31bpomkck6qnkaa60!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/a873ebf05f7623d18cc1745cd8eaa92b/1040g008318k1mq4mgs0g5n31bpomkck6u62lekg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/5bd30c8eaac52fb5f8c5ccb4dcbdcd4e/1040g008318k1mq4mgs105n31bpomkck6b7kbi40!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/22f6e699910c6484964eb0d39d8c5e72/1040g008318k1mq4mgs1g5n31bpomkck6led3kbo!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/765878bd0494f05cbe3a8a0865a7d56b/1040g008318k1mq4mgs205n31bpomkck66v82j7g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/99b480f0d0a7f62ffc0099dfe6eb39f6/1040g008318k1mq4mgs2g5n31bpomkck6344rci0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/e671bccf2a3dd3ea31c1949a3e05cd80/1040g008318k1mq4mgs305n31bpomkck6abqlmfg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/735b3ee30a2006f9bf54ca494f2782bc/1040g008318k1mq4mgs3g5n31bpomkck6j3lj1n8!nd_dft_wgth_webp_3']</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/66b9a0160000000025032e89?xsec_token=ABd2mFiQbEpaLgTkyJck3xd8W2DFebj3JtdzbsarUNDbE=</t>
+          <t>https://www.xiaohongshu.com/explore/66b9a0160000000025032e89?xsec_token=ABd2mFiQbEpaLgTkyJck3xdwUQbDGW5WYjsd9Mu_DS0ls=</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/9cda2695f5b3b40ca21e11a5a6b17985/1040g2sg316cv0kotgqd05n31bpomkck6e0q96cg!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/20ff154c4d3a931cda7e3897535418a0/1040g2sg316cv0kotgqb05n31bpomkck6keaij00!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/d5882f5604f451c3584357b2d526f7e6/1040g2sg316cv0kotgqcg5n31bpomkck6tbkk0t0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/3255bdd2b0a162928b18a7e4ba35f9ce/1040g2sg316cv0kotgqag5n31bpomkck633thg4o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/af8091b68b96cb695610d1a7f5fd3bae/1040g2sg316cv0kotgqc05n31bpomkck68m8l0eg!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/da4372ce31ff20370f303839a4c14e50/1040g2sg316cv0kotgq705n31bpomkck6fb1quog!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/8214968afe5e5ef8e36195cd791f1e14/1040g2sg316cv0kotgqbg5n31bpomkck6nq5sv10!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/852d30fa456720eeb8122805d0aa09af/1040g2sg316cv0kotgq8g5n31bpomkck6632ie7g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/ea05613f2688f8d28b1160ea4b2f5bba/1040g2sg316cv0kotgqa05n31bpomkck661r8ato!nd_dft_wlteh_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/fcce68ca3a6936501f05a2f1dd0c4abb/1040g2sg316cv0kotgqd05n31bpomkck6e0q96cg!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/2b83c557b4594d280c79c29449f94e1f/1040g2sg316cv0kotgqb05n31bpomkck6keaij00!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/3717577bbf3e6175b4ae5e7e3ebbe91f/1040g2sg316cv0kotgqcg5n31bpomkck6tbkk0t0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/fa28b48cac80f54b0ba6dd2ad886bc6e/1040g2sg316cv0kotgqag5n31bpomkck633thg4o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/33fcd7939898b985a6f141585fa104af/1040g2sg316cv0kotgqc05n31bpomkck68m8l0eg!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/550d7100eb9ff4e51d024dfd3d666774/1040g2sg316cv0kotgq705n31bpomkck6fb1quog!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/9f1ed4b57049595e42e9bde24cf88ed1/1040g2sg316cv0kotgqbg5n31bpomkck6nq5sv10!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/e7e9ce1cde59ae09aaafc67ee1f53415/1040g2sg316cv0kotgq8g5n31bpomkck6632ie7g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/eaa969731d1a51c3cfc6dee237775aa2/1040g2sg316cv0kotgqa05n31bpomkck661r8ato!nd_dft_wlteh_webp_3']</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/6692179900000000250032e1?xsec_token=ABqDPRU0Mz5PaWvA4ReeNPxIMWtUG5nm755JuRXEBpW20=</t>
+          <t>https://www.xiaohongshu.com/explore/6692179900000000250032e1?xsec_token=ABqDPRU0Mz5PaWvA4ReeNPxKok5PKkUM_PdjDsn5pL1eA=</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/92d03b74da923a460675b3588853bd50/1040g0083156bjuo1gs005n31bpomkck6gmr8r78!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/e1fbe7c906e3343b8b9a2dc64df22015/1040g0083156bjuo20s305n31bpomkck6g6eu6jg!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/a09119bef21c03e2548904d82fbfe89b/1040g0083156bjuo20s205n31bpomkck69m268c0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/b7729bce15af16e71f7638fbcdcd52c3/1040g0083156bjuo20s1g5n31bpomkck6t0udn60!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/7856e21b3b94bfc61b500fa5fa24558a/1040g0083156bjuo1gs305n31bpomkck6juiscqg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/5e9d5d8aca95e13ad897da248d42ee51/1040g0083156bjuo20s105n31bpomkck6nit7kao!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/c4e405ec07b1b05d9b8a4bf615340e03/1040g0083156bjuo20s0g5n31bpomkck6m3jdduo!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/50cba12315ddc209762e20e940778486/1040g0083156bjuo20s005n31bpomkck6dslnpfg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/cc79ff6624ee62c1e44906cd277dfea5/1040g0083156bjuo1gs0g5n31bpomkck6el5vbog!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/b229753ebc515e1b39a45e647387d203/1040g0083156bjuo1gs2g5n31bpomkck6c1dgh8o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/fad1d3cf04f8580a1ca98af989da97d4/1040g0083156bjuo1gs105n31bpomkck6pggd060!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/3dc6a301a7458e99d2a0a73cb780fcb5/1040g0083156bjuo1gs205n31bpomkck6r62dvr0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/0354fb8f490f1b5b61ef953cb354c857/1040g0083156bjuo1gs1g5n31bpomkck6m73ng98!nd_dft_wgth_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/95f6cf414444e1ec5d8b2e15e0f7b92f/1040g0083156bjuo1gs005n31bpomkck6gmr8r78!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/7b5ed7219257c532d3f9c41cc929ee9d/1040g0083156bjuo20s305n31bpomkck6g6eu6jg!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/435be6023fc18010015946c4323f11a9/1040g0083156bjuo20s205n31bpomkck69m268c0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/122ba55ea7c29994f1a12beffa0346c1/1040g0083156bjuo20s1g5n31bpomkck6t0udn60!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/1ec0225221d3eab28b737d6958000731/1040g0083156bjuo1gs305n31bpomkck6juiscqg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/a32ecb4571d56c12023dd8e42a5ac69a/1040g0083156bjuo20s105n31bpomkck6nit7kao!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/be3ad5ef24ebf5c3769fbed77ffc3d2c/1040g0083156bjuo20s0g5n31bpomkck6m3jdduo!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/21af922dc2adca807cc80b1862aa8083/1040g0083156bjuo20s005n31bpomkck6dslnpfg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/ae1962d2f819d4145532f1f7721cb267/1040g0083156bjuo1gs0g5n31bpomkck6el5vbog!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/569512e5e61af7199f28db0088d18026/1040g0083156bjuo1gs2g5n31bpomkck6c1dgh8o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/284c25573d0c21a8fdc58568c50961c1/1040g0083156bjuo1gs105n31bpomkck6pggd060!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/ea46c662a924810f9f182f47286e099b/1040g0083156bjuo1gs205n31bpomkck6r62dvr0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/1bc478a9f665563b7b8546c66a78934c/1040g0083156bjuo1gs1g5n31bpomkck6m73ng98!nd_dft_wgth_webp_3']</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/666599e2000000000d00d11b?xsec_token=ABkF2GcBh5l7ZgrShx6NQjvG7U6eBIZwLq99wtzzShCrM=</t>
+          <t>https://www.xiaohongshu.com/explore/666599e2000000000d00d11b?xsec_token=ABkF2GcBh5l7ZgrShx6NQjvMBx8dCVUBncpdcQ4MAXt9M=</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/e104f82037e1149ea14644a72510c813/1040g008313qt8pl2h81g5n31bpomkck664ccago!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/37e6807d53f25964a9d15b75cf9e3f7b/1040g008313qt8pl2h8105n31bpomkck65vgjnvg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/ff0614b4bcac49ad32a9d3081e3d13db/1040g008313qt8pl2h80g5n31bpomkck6puqks5o!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/74ba01a2c84076ae26d6cd4d2322d7d6/1040g008313qt8pl2183g5n31bpomkck6uuga6g8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/62db5d14ebcd4a84d6231f9cc82c8d6e/1040g008313qt8pl2184g5n31bpomkck6jvills0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/71a054305fb41fd6360654acd9a01b12/1040g008313qt8pl2h8005n31bpomkck6gd4gt38!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/60c07537913de71ec4fb788ff84abbf3/1040g008313qt8pl218405n31bpomkck68g6v1s0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/895397f36961feb0c836aa26297b2e04/1040g008313qt8pl218305n31bpomkck6g5tet1o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/bbbd5162d20b8eb3c3a8e33b605e8d4e/1040g008313qt8pl2182g5n31bpomkck6v97gel0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/c233ceea2508a8b5cba3524f12d8a153/1040g008313qt8pl2181g5n31bpomkck6bi1hqrg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/a31232edf0df4e0610343074bd7906c9/1040g008313qt8pl218205n31bpomkck67u6tg4o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/20419b2ee3af3fd70fb26293f4f55e3f/1040g008313qt8pl2180g5n31bpomkck6pui11k0!nd_dft_wlteh_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/287e7b26ff02ff58b3a84df911c1e75a/1040g008313qt8pl2h81g5n31bpomkck664ccago!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/f3dea4d84b1c013211ea7048e6643b88/1040g008313qt8pl2h8105n31bpomkck65vgjnvg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/11c8f94805130adef321c077ae078223/1040g008313qt8pl2h80g5n31bpomkck6puqks5o!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/c1d1ce230e6ea46ce3f6aa8890e6d699/1040g008313qt8pl2183g5n31bpomkck6uuga6g8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/799004d410fcf56aaf57d1371ad63904/1040g008313qt8pl2184g5n31bpomkck6jvills0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/e15afb2477ee94bab7eac025dd2f269a/1040g008313qt8pl2h8005n31bpomkck6gd4gt38!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/4da96df6602098c44eedc6e7170490e7/1040g008313qt8pl218405n31bpomkck68g6v1s0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/f55ccba0f82d7032f3ab76eced62b6fc/1040g008313qt8pl218305n31bpomkck6g5tet1o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/320266a03a590e55c10efc7c14914bdd/1040g008313qt8pl2182g5n31bpomkck6v97gel0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/8dcdba45d3af87b53563ea24b598d388/1040g008313qt8pl2181g5n31bpomkck6bi1hqrg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/487ca16941a8f8f1ffd1aebc35a68bd0/1040g008313qt8pl218205n31bpomkck67u6tg4o!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/e843a5521a7a4e440bcc57336b7f3850/1040g008313qt8pl2180g5n31bpomkck6pui11k0!nd_dft_wlteh_webp_3']</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/6611043a000000001a00cde2?xsec_token=AB4cKqBN9yDZkrODFQZZe-qbNpl6XYmT2-TWcuzhP46vM=</t>
+          <t>https://www.xiaohongshu.com/explore/6611043a000000001a00cde2?xsec_token=AB4cKqBN9yDZkrODFQZZe-qUdmrZ9soKOEwf9BVV9bb4w=</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/4ed856b33216d915805be378b83aee39/1040g2sg3118a0av66o6g5n31bpomkck6b0heqmg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/03e942733973440ba1b42b51093a5f8f/1040g2sg3118a0av66o605n31bpomkck6cqm5nr8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/44b35765b7166edc618dda11c8eb777f/1040g2sg3118a0av66o505n31bpomkck6d3nnopo!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/afcdd94f647da094a56d00acdc9d2cfb/1040g2sg3118a0av66o405n31bpomkck6m9avd68!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/a7547217cfb50b4c1c9118cfe1609ae4/1040g2sg3118a0av66o3g5n31bpomkck6i74t7go!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/fbd41ea4a1a0ced073376873cbe24ffd/1040g2sg3118a0av66o205n31bpomkck6jv75kg0!nd_dft_wgth_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/7468b4544a169e38a544ea75df8dd16c/1040g2sg3118a0av66o6g5n31bpomkck6b0heqmg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/81d7502825cb75559a1f8471219faece/1040g2sg3118a0av66o605n31bpomkck6cqm5nr8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/7acd9d4ffe5b9dac5d78b7c59040001f/1040g2sg3118a0av66o505n31bpomkck6d3nnopo!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/397fef0d6960025d14eb4998956d6195/1040g2sg3118a0av66o405n31bpomkck6m9avd68!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/2ba6923aa3f2b73ca136c97df83899d6/1040g2sg3118a0av66o3g5n31bpomkck6i74t7go!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/d4cb4a7eb8e0311299b8f1540cba1b3b/1040g2sg3118a0av66o205n31bpomkck6jv75kg0!nd_dft_wgth_webp_3']</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/65f827aa000000000d00e73e?xsec_token=ABZia3bKSDukB76pXKyeJri94uX3HRmraviUeXSwdeEeg=</t>
+          <t>https://www.xiaohongshu.com/explore/65f827aa000000000d00e73e?xsec_token=ABZia3bKSDukB76pXKyeJri6spLWc6Z-GiufRSsAyZWc8=</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/5be877adb44cbc346c4f482282c44acf/1040g008310g12ob6mm605n31bpomkck6k3qqh6g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/a32bada4757712dcb4867b44ab5be671/1040g008310g12ob6mm6g5n31bpomkck6sj81rug!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/fe1935a2ce1e16545c4e902989cda461/1040g008310g12ob6mm5g5n31bpomkck6r40m9ig!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/f34c6af7703ad926c0ef096bc6c4d064/1040g008310g12ob6mm405n31bpomkck67neurk0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/7397b778bb709331b2757f369e53fd1c/1040g008310g12ob6mm305n31bpomkck6jt6hop8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/d3cc2e7600c5af448357c298d346cb42/1040g008310g12ob6mm205n31bpomkck6o7f1t28!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/65abdfe713e41600adb57d2900ec8ea1/1040g008310g12ob6mm1g5n31bpomkck6crafeg8!nd_dft_wlteh_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/79763ffb4081868e1f9faee0d9516866/1040g008310g12ob6mm605n31bpomkck6k3qqh6g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/0de944c32bdc39c76fa6ae5a076de83a/1040g008310g12ob6mm6g5n31bpomkck6sj81rug!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/d1bf85b367e718c9394f77fb1a4edcf5/1040g008310g12ob6mm5g5n31bpomkck6r40m9ig!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/e10fd49514ef1c58a057e7940ebfb099/1040g008310g12ob6mm405n31bpomkck67neurk0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/2a46d61d31a86492565de422216f32a1/1040g008310g12ob6mm305n31bpomkck6jt6hop8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/1a626c87c8aced45db922305751110b6/1040g008310g12ob6mm205n31bpomkck6o7f1t28!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/ac0497b73e0c8681d9ebafa0eb58f462/1040g008310g12ob6mm1g5n31bpomkck6crafeg8!nd_dft_wlteh_webp_3']</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/65f5396f000000001203c0ae?xsec_token=ABpxL2V5V_yqTXANwVzdBKfTNvv4Aws4OnOqXI38MLSOw=</t>
+          <t>https://www.xiaohongshu.com/explore/65f5396f000000001203c0ae?xsec_token=ABpxL2V5V_yqTXANwVzdBKfY-_GKmG8aScq5fjwLp2L8U=</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/784980ada23fe87e9c4899214d5d3613/1040g2sg310d5g4ormc5g5n31bpomkck6p5fo0l0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/265ea5e24a71015fbbbad9688c6e0e20/1040g2sg310d5g4ormc505n31bpomkck65k8vevo!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/bbf67409fe0ec07ce9e426c2a608713b/1040g2sg310d5g4ormc4g5n31bpomkck6a43a1b0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/334620c159aaa391d2cec2c21dd3f096/1040g2sg310d5g4ormc405n31bpomkck6is6k36g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/701191b20c733a8e8eda84c00faa46c7/1040g2sg310d5g4ormc305n31bpomkck6jhb21q8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/c17831f22772babfc2f526a37afed777/1040g2sg310d5g4ormc205n31bpomkck640bbsmo!nd_dft_wlteh_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/2cfe26f195d197ff68e2a88a47aaeff8/1040g2sg310d5g4ormc5g5n31bpomkck6p5fo0l0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/396d2cf8d58db87286a17cc3df3739ce/1040g2sg310d5g4ormc505n31bpomkck65k8vevo!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/04018eeea940896bdfc187cd1b6bf3bc/1040g2sg310d5g4ormc4g5n31bpomkck6a43a1b0!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/250f6947c9d2ff2a156c53bd8e289589/1040g2sg310d5g4ormc405n31bpomkck6is6k36g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/fd3db5221004553bcfce3c287fc99c57/1040g2sg310d5g4ormc305n31bpomkck6jhb21q8!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/21180450c226103cfa48f1a5ab0ba5c9/1040g2sg310d5g4ormc205n31bpomkck640bbsmo!nd_dft_wlteh_webp_3']</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/65ec804300000000010292c6?xsec_token=ABQFfVPD4_iO-f56j4MJz_7CwM9V_e9efMJKi50FHszH0=</t>
+          <t>https://www.xiaohongshu.com/explore/65ec804300000000010292c6?xsec_token=ABQFfVPD4_iO-f56j4MJz_7BdArjwsdIFxCjMCu9MIhLM=</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/76d3a8a61024cf3e2ea873b880993c34/1040g2sg3104kspvsm26g5n31bpomkck67ktms2g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/5aa1291ed105ea773f59dfc82d0582d4/1040g2sg3104kspvsm2505n31bpomkck6pknudk0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/82fa46569a200281ce7ada471bc82a1e/1040g2sg3104kspvsm23g5n31bpomkck6n2qenlo!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/5295f036978bbf5885b8c707678b88f9/1040g2sg3104kspvsm25g5n31bpomkck6n4cr860!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/35f0b22a8f08f85fba6821eead321935/1040g2sg3104kspvsm22g5n31bpomkck6ojskma0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/4030158b717cf7c0841caeec4dc561e9/1040g2sg3104kspvsm21g5n31bpomkck6ubrrseg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/1a9259bce08b1141865728e3e95b5a21/1040g2sg3104kspvsm2305n31bpomkck6rh1tg08!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/5f1cea0c80647b89fc316aeeaa64ba7f/1040g2sg3104kspvsm2105n31bpomkck6epreu9o!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/a405e9ddae7e7e5598a755282428d530/1040g2sg3104kspvsm20g5n31bpomkck6uu1gvbo!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/f5ba86b180ce108f6394133a68b4a431/1040g2sg3104kspvsm2205n31bpomkck6tq4idj8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/b82f10bcb1c35474b3a43f81441068cd/1040g2sg3104kspvsm2005n31bpomkck6o0hlr28!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/fa17de44acf9c8eb8c6ba1d8075fca81/1040g2sg3104kspvsm2605n31bpomkck6mqcpp2g!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/ba2e390b68f798b2080afb4f1a7fbf76/1040g2sg3104kspvsm24g5n31bpomkck61oga080!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/f9a5afde8311be67608fc8a7e1f16228/1040g2sg3104kspvsm2405n31bpomkck62u9c4e0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/4772bb73941f46f6e260402e338057b0/1040g2sg3104ksrdjm4405n31bpomkck6lqd6t20!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/644b114961318a957d230fc518208cd6/1040g2sg3104ksrdjm42g5n31bpomkck6f4j07q8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/3ec4260ae472d71235ec6211aefb1eaa/1040g2sg3104ksrdjm4205n31bpomkck6p356lug!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601201558/fa4fc3b15e05f91ad541e5eea608360e/1040g2sg3104ksrdjm4005n31bpomkck6ct77rq0!nd_dft_wgth_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/aabd0450ef38b362b5249ddf70b8e9cf/1040g2sg3104kspvsm26g5n31bpomkck67ktms2g!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/1cb2094ebcebaf72cf4da59189e03be4/1040g2sg3104kspvsm2505n31bpomkck6pknudk0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/208c14ca4b6df23f17a77fe4d4e2163b/1040g2sg3104kspvsm23g5n31bpomkck6n2qenlo!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/4cd96abeb203b3554be94205f5012617/1040g2sg3104kspvsm25g5n31bpomkck6n4cr860!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/4011fd2a5c44b98d48e59e2b90441d53/1040g2sg3104kspvsm22g5n31bpomkck6ojskma0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/08db72ce8caac8ea21674c96bcbe9354/1040g2sg3104kspvsm21g5n31bpomkck6ubrrseg!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/a6fde37b3c59cc1e82efac68f2100ad4/1040g2sg3104kspvsm2305n31bpomkck6rh1tg08!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/a1275c8dcf7cfed768af38fdd4faf84f/1040g2sg3104kspvsm2105n31bpomkck6epreu9o!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/22976a28f3ccf651ac4a3e581f82602a/1040g2sg3104kspvsm20g5n31bpomkck6uu1gvbo!nd_dft_wlteh_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/2f213d585ae283704f9de272893ff342/1040g2sg3104kspvsm2205n31bpomkck6tq4idj8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/cfb66e795f4dc0e761d84498b2cc3c87/1040g2sg3104kspvsm2005n31bpomkck6o0hlr28!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/9c681ccedde124e3cba3cb92f1173300/1040g2sg3104kspvsm2605n31bpomkck6mqcpp2g!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/b933ca0b86b9e030cc72801d636e057c/1040g2sg3104kspvsm24g5n31bpomkck61oga080!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/81e4efd53e517b464454ba8f822804ac/1040g2sg3104kspvsm2405n31bpomkck62u9c4e0!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/29d488cc9381124c6a125b32b3dc325e/1040g2sg3104ksrdjm4405n31bpomkck6lqd6t20!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/af87ff440d638cd6c7aaa78520aa57a3/1040g2sg3104ksrdjm42g5n31bpomkck6f4j07q8!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/25424a4727ed5a943becb8c44e6543c3/1040g2sg3104ksrdjm4205n31bpomkck6p356lug!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202601211816/4ebe87096c3b9c5744067045cd6deb46/1040g2sg3104ksrdjm4005n31bpomkck6ct77rq0!nd_dft_wgth_webp_3']</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/65d2405e0000000007007855?xsec_token=AB0ecVcgW8wKs7sKq1dizuLI81714GPCf-A6DkXJT4rb8=</t>
+          <t>https://www.xiaohongshu.com/explore/65d2405e0000000007007855?xsec_token=AB0ecVcgW8wKs7sKq1dizuLMpnyp_waHPjee7KQxnNYpY=</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>['http://sns-webpic-qc.xhscdn.com/202601201558/02a88fc1ee3bbc89ee5ad1f9d945e7b7/1040g2sg30vb0j918l66g5n31bpomkck6pql7kgg!nd_dft_wlteh_webp_3']</t>
+          <t>['http://sns-webpic-qc.xhscdn.com/202601211816/ff75c79ded5b5bd6ba113e166808576a/1040g2sg30vb0j918l66g5n31bpomkck6pql7kgg!nd_dft_wlteh_webp_3']</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
